--- a/ewatch_data/meter_export_load_off.xlsx
+++ b/ewatch_data/meter_export_load_off.xlsx
@@ -19,7 +19,7 @@
     <t>Organisation: Malaviya National Institute of Technology Jaipur</t>
   </si>
   <si>
-    <t xml:space="preserve">Duration(dd/mm/yyyy): 04/06/2026 </t>
+    <t xml:space="preserve">Duration(dd/mm/yyyy): 08/06/2026 </t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -418,7 +418,7 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LNote : Blank column/s = data unavailable 
- Printed Date : 05/06/2026 06:27:39 PM 
+ Printed Date : 09/06/2026 01:39:03 PM 
  Daily meter reading will be the first reading of the day where meter is successfully connected.</oddFooter>
   </headerFooter>
 </worksheet>
